--- a/results/Experiment Results.xlsx
+++ b/results/Experiment Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjalilitorkamani2/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjalilitorkamani2/Codes/Assertion-Generation-Tool-Public-Thesis-Repo/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384A99EC-9FB5-3B45-B1D4-0C49A7C77B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD9661-BE6E-5947-8897-DA5CA533E330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4340" yWindow="-20980" windowWidth="38400" windowHeight="19700" activeTab="1" xr2:uid="{DA674940-60FC-794E-B56D-A055D95D16AA}"/>
+    <workbookView xWindow="-4340" yWindow="-20980" windowWidth="38400" windowHeight="19700" xr2:uid="{DA674940-60FC-794E-B56D-A055D95D16AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data - GPT-4o" sheetId="6" r:id="rId1"/>
@@ -40,18 +40,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="50">
   <si>
     <t>baseline</t>
-  </si>
-  <si>
-    <t>Assertron (A, A)</t>
-  </si>
-  <si>
-    <t>Assertron (B, B)</t>
-  </si>
-  <si>
-    <t>Assertron (C, C)</t>
-  </si>
-  <si>
-    <t>Assertron (D, D)</t>
   </si>
   <si>
     <t>AssertionFul Records</t>
@@ -187,6 +175,18 @@
   </si>
   <si>
     <t>Model D</t>
+  </si>
+  <si>
+    <t>Tool (A, A)</t>
+  </si>
+  <si>
+    <t>Tool (B, B)</t>
+  </si>
+  <si>
+    <t>Tool (C, C)</t>
+  </si>
+  <si>
+    <t>Tool (D, D)</t>
   </si>
 </sst>
 </file>
@@ -22830,21 +22830,21 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>59</v>
@@ -22864,7 +22864,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -22884,7 +22884,7 @@
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>55</v>
@@ -22904,7 +22904,7 @@
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -22924,7 +22924,7 @@
     </row>
     <row r="6" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <f>D45-0</f>
@@ -22949,7 +22949,7 @@
     </row>
     <row r="7" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <f>B6-20.333</f>
@@ -22974,7 +22974,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <f>B7-6.666</f>
@@ -22999,7 +22999,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>224.333</v>
@@ -23019,7 +23019,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>142.333</v>
@@ -23039,7 +23039,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2">
         <f t="shared" ref="B11:F11" si="0">B10/B9*100</f>
@@ -23064,7 +23064,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
         <v>264.33300000000003</v>
@@ -23084,7 +23084,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2">
         <v>367.33300000000003</v>
@@ -23104,7 +23104,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <f t="shared" ref="B14:F14" si="1">B12+B13</f>
@@ -23129,7 +23129,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2">
         <f t="shared" ref="B15:F15" si="2">(B16/(B16+B17)*100)</f>
@@ -23154,7 +23154,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2">
         <v>256</v>
@@ -23174,7 +23174,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
         <v>288.33300000000003</v>
@@ -23194,7 +23194,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
         <f t="shared" ref="B18:F18" si="3">B17+B16</f>
@@ -23219,7 +23219,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
         <f t="shared" ref="B19:F19" si="4">B18/B14*100</f>
@@ -23244,7 +23244,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
         <v>8.3330000000000002</v>
@@ -23264,7 +23264,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>79</v>
@@ -23284,7 +23284,7 @@
     </row>
     <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2">
         <v>1</v>
@@ -23304,7 +23304,7 @@
     </row>
     <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2">
         <v>0.71599999999999997</v>
@@ -23324,7 +23324,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>0.63500000000000001</v>
@@ -23344,7 +23344,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>30.422000000000001</v>
@@ -23364,7 +23364,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>44.006</v>
@@ -23384,7 +23384,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>39376.35</v>
@@ -23404,7 +23404,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>0.49</v>
@@ -23424,7 +23424,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>0.51100000000000001</v>
@@ -23444,7 +23444,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>0.55800000000000005</v>
@@ -23464,7 +23464,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>0.52</v>
@@ -23484,7 +23484,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>0.44600000000000001</v>
@@ -23504,7 +23504,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>0.95799999999999996</v>
@@ -23524,7 +23524,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>0.36</v>
@@ -23544,7 +23544,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>0.11899999999999999</v>
@@ -23564,7 +23564,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>3.5000000000000003E-2</v>
@@ -23584,7 +23584,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>0.54700000000000004</v>
@@ -23604,7 +23604,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>0.36599999999999999</v>
@@ -23624,7 +23624,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>0.97099999999999997</v>
@@ -23644,7 +23644,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>0.38800000000000001</v>
@@ -23671,24 +23671,24 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2">
         <v>60</v>
@@ -23818,8 +23818,7 @@
     <col min="4" max="4" width="15.83203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.1640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="9" max="23" width="0" style="2" hidden="1"/>
+    <col min="7" max="23" width="0" style="2" hidden="1" customWidth="1"/>
     <col min="24" max="16384" width="10.83203125" style="2" hidden="1"/>
   </cols>
   <sheetData>
@@ -23828,21 +23827,21 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>59</v>
@@ -23862,7 +23861,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -23882,7 +23881,7 @@
     </row>
     <row r="4" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>55</v>
@@ -23902,7 +23901,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
@@ -23922,7 +23921,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2">
         <f>D45-0</f>
@@ -23947,7 +23946,7 @@
     </row>
     <row r="7" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <f>B6-37</f>
@@ -23972,7 +23971,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2">
         <f>B7-16.333</f>
@@ -23997,7 +23996,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B9" s="5">
         <v>607</v>
@@ -24017,7 +24016,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" s="5">
         <v>234</v>
@@ -24037,7 +24036,7 @@
     </row>
     <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" s="5">
         <f t="shared" ref="B11:F11" si="0">B10/B9*100</f>
@@ -24062,7 +24061,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B12" s="5">
         <v>429.33300000000003</v>
@@ -24082,7 +24081,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5">
         <v>694.66600000000005</v>
@@ -24102,7 +24101,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5">
         <f>B12+B13</f>
@@ -24127,7 +24126,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5">
         <f>(B16/(B16+B17)*100)</f>
@@ -24152,7 +24151,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="5">
         <v>325.33300000000003</v>
@@ -24172,7 +24171,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5">
         <v>551.66600000000005</v>
@@ -24192,7 +24191,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5">
         <f>B16+B17</f>
@@ -24217,7 +24216,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5">
         <f>B18/B14*100</f>
@@ -24242,7 +24241,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" s="5">
         <v>104</v>
@@ -24262,7 +24261,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B21" s="5">
         <v>143</v>
@@ -24282,7 +24281,7 @@
     </row>
     <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -24302,7 +24301,7 @@
     </row>
     <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5">
         <v>0.51</v>
@@ -24322,7 +24321,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>0.38500000000000001</v>
@@ -24342,7 +24341,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
         <v>36.036000000000001</v>
@@ -24362,7 +24361,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2">
         <v>44.006</v>
@@ -24382,7 +24381,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2">
         <v>45433.983</v>
@@ -24402,7 +24401,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>0.41099999999999998</v>
@@ -24422,7 +24421,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2">
         <v>0.45300000000000001</v>
@@ -24442,7 +24441,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>0.48899999999999999</v>
@@ -24462,7 +24461,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2">
         <v>0.46700000000000003</v>
@@ -24482,7 +24481,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
         <v>0.4</v>
@@ -24502,7 +24501,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B33" s="2">
         <v>1.1379999999999999</v>
@@ -24522,7 +24521,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2">
         <v>0.30399999999999999</v>
@@ -24542,7 +24541,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
         <v>0.14599999999999999</v>
@@ -24562,7 +24561,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
         <v>0.01</v>
@@ -24582,7 +24581,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
         <v>0.49199999999999999</v>
@@ -24602,7 +24601,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
         <v>0.32</v>
@@ -24622,7 +24621,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
         <v>0.73699999999999999</v>
@@ -24642,7 +24641,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
         <v>0.33600000000000002</v>
@@ -24669,24 +24668,24 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D45" s="2">
         <v>60</v>

--- a/results/Experiment Results.xlsx
+++ b/results/Experiment Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mjalilitorkamani2/Codes/Assertion-Generation-Tool-Public-Thesis-Repo/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD9661-BE6E-5947-8897-DA5CA533E330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC29563-F3E2-F94A-97EE-2220B8CF6CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4340" yWindow="-20980" windowWidth="38400" windowHeight="19700" xr2:uid="{DA674940-60FC-794E-B56D-A055D95D16AA}"/>
+    <workbookView xWindow="-4340" yWindow="-20980" windowWidth="38400" windowHeight="19700" activeTab="1" xr2:uid="{DA674940-60FC-794E-B56D-A055D95D16AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data - GPT-4o" sheetId="6" r:id="rId1"/>
@@ -177,16 +177,16 @@
     <t>Model D</t>
   </si>
   <si>
-    <t>Tool (A, A)</t>
+    <t>Tool (FT: A, Inp: A)</t>
   </si>
   <si>
-    <t>Tool (B, B)</t>
+    <t>Tool (FT: B, Inp: B)</t>
   </si>
   <si>
-    <t>Tool (C, C)</t>
+    <t>Tool (FT: C, Inp: C)</t>
   </si>
   <si>
-    <t>Tool (D, D)</t>
+    <t>Tool (FT: D, Inp: D)</t>
   </si>
 </sst>
 </file>
